--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Nevado de Chillan Vn.</t>
@@ -551,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -579,9 +582,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -672,13 +676,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <v>-36.86333</v>
@@ -720,12 +727,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>-36.86333</v>
@@ -764,12 +771,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>-36.86333</v>
@@ -808,12 +815,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>-37.82667</v>
@@ -855,12 +862,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>-37.85</v>
@@ -899,12 +906,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>-37.85</v>
@@ -943,12 +950,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>-37.85</v>
@@ -987,12 +994,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>-37.85</v>
@@ -1034,12 +1041,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>-37.99123</v>
@@ -1081,12 +1088,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>-38.06739</v>
@@ -1128,12 +1135,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12">
         <v>-38.47289</v>
@@ -1172,12 +1179,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>-38.18931</v>
@@ -1219,12 +1226,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>-38.23439</v>
@@ -1266,12 +1273,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>-38.31</v>
@@ -1310,12 +1317,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>-38.5833</v>
@@ -1356,10 +1363,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>-38.58015</v>
@@ -1403,10 +1410,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>-38.95637</v>
@@ -1450,10 +1457,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>-39.14</v>
@@ -1497,10 +1504,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>-39.21944</v>
@@ -1544,10 +1551,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>-39.32877</v>
@@ -1591,10 +1598,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>-39.34004</v>
@@ -1638,10 +1645,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <v>-39.42105</v>
@@ -1685,10 +1692,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <v>-39.42062</v>
@@ -1732,10 +1739,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25">
         <v>-39.6</v>
@@ -1779,10 +1786,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <v>-39.635</v>
@@ -1826,10 +1833,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>-39.74</v>
@@ -1873,10 +1880,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>-40.19396</v>
@@ -1920,10 +1927,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>-40.71223</v>
@@ -1967,10 +1974,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>-40.73555</v>
@@ -2014,10 +2021,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>-40.85889</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="60">
   <si>
     <t>location</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>LOFS</t>
+  </si>
+  <si>
+    <t>Andesite</t>
   </si>
 </sst>
 </file>
@@ -693,6 +696,9 @@
       <c r="D2">
         <v>-71.37667</v>
       </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
       <c r="H2">
         <v>68</v>
       </c>
@@ -740,6 +746,9 @@
       <c r="D3">
         <v>-71.37667</v>
       </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
       <c r="H3">
         <v>82</v>
       </c>
@@ -784,6 +793,9 @@
       <c r="D4">
         <v>-71.37667</v>
       </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
       <c r="H4">
         <v>91</v>
       </c>
@@ -828,6 +840,9 @@
       <c r="D5">
         <v>-71.13</v>
       </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
       <c r="H5">
         <v>45</v>
       </c>
@@ -875,6 +890,9 @@
       <c r="D6">
         <v>-71.17</v>
       </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
       <c r="H6">
         <v>87</v>
       </c>
@@ -919,6 +937,9 @@
       <c r="D7">
         <v>-71.17</v>
       </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
       <c r="H7">
         <v>93</v>
       </c>
@@ -963,6 +984,9 @@
       <c r="D8">
         <v>-71.17</v>
       </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
       <c r="H8">
         <v>88</v>
       </c>
@@ -1007,6 +1031,9 @@
       <c r="D9">
         <v>-71.17</v>
       </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
       <c r="H9">
         <v>47</v>
       </c>
@@ -1054,6 +1081,9 @@
       <c r="D10">
         <v>-71.53136000000001</v>
       </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
       <c r="H10">
         <v>78</v>
       </c>
@@ -1101,6 +1131,9 @@
       <c r="D11">
         <v>-71.71277000000001</v>
       </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
       <c r="H11">
         <v>38.5</v>
       </c>
@@ -1148,6 +1181,9 @@
       <c r="D12">
         <v>-71.36324</v>
       </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
       <c r="H12">
         <v>82</v>
       </c>
@@ -1192,6 +1228,9 @@
       <c r="D13">
         <v>-71.0365</v>
       </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
       <c r="H13">
         <v>36</v>
       </c>
@@ -1239,6 +1278,9 @@
       <c r="D14">
         <v>-71.72808999999999</v>
       </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
       <c r="H14">
         <v>85.5</v>
       </c>
@@ -1286,6 +1328,9 @@
       <c r="D15">
         <v>-71.645</v>
       </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
       <c r="H15">
         <v>92</v>
       </c>
@@ -1330,6 +1375,9 @@
       <c r="D16">
         <v>-71.58329999999999</v>
       </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
       <c r="H16">
         <v>87</v>
       </c>
@@ -1374,6 +1422,9 @@
       <c r="D17">
         <v>-71.62808</v>
       </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
       <c r="H17">
         <v>35</v>
       </c>
@@ -1421,6 +1472,9 @@
       <c r="D18">
         <v>-71.70944</v>
       </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
       <c r="H18">
         <v>45</v>
       </c>
@@ -1468,6 +1522,9 @@
       <c r="D19">
         <v>-71.48999999999999</v>
       </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
       <c r="H19">
         <v>51</v>
       </c>
@@ -1515,6 +1572,9 @@
       <c r="D20">
         <v>-71.69588</v>
       </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
       <c r="H20">
         <v>45</v>
       </c>
@@ -1562,6 +1622,9 @@
       <c r="D21">
         <v>-71.72086</v>
       </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
       <c r="H21">
         <v>42</v>
       </c>
@@ -1609,6 +1672,9 @@
       <c r="D22">
         <v>-71.69108</v>
       </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
       <c r="H22">
         <v>40</v>
       </c>
@@ -1656,6 +1722,9 @@
       <c r="D23">
         <v>-71.78619</v>
       </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
       <c r="H23">
         <v>50</v>
       </c>
@@ -1703,6 +1772,9 @@
       <c r="D24">
         <v>-71.67094</v>
       </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
       <c r="H24">
         <v>37</v>
       </c>
@@ -1750,6 +1822,9 @@
       <c r="D25">
         <v>-71.95</v>
       </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
       <c r="H25">
         <v>50</v>
       </c>
@@ -1797,6 +1872,9 @@
       <c r="D26">
         <v>-71.9233</v>
       </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
       <c r="H26">
         <v>74.59999999999999</v>
       </c>
@@ -1844,6 +1922,9 @@
       <c r="D27">
         <v>-71.84999999999999</v>
       </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
       <c r="H27">
         <v>37.2</v>
       </c>
@@ -1891,6 +1972,9 @@
       <c r="D28">
         <v>-71.9345</v>
       </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
       <c r="H28">
         <v>82.5</v>
       </c>
@@ -1938,6 +2022,9 @@
       <c r="D29">
         <v>-72.32695</v>
       </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
       <c r="H29">
         <v>60</v>
       </c>
@@ -1985,6 +2072,9 @@
       <c r="D30">
         <v>-72.30749</v>
       </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
       <c r="H30">
         <v>66</v>
       </c>
@@ -2031,6 +2121,9 @@
       </c>
       <c r="D31">
         <v>-72.22278</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
       </c>
       <c r="H31">
         <v>80</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/before_conversion_chile_mapped_readable.xlsx
@@ -803,10 +803,13 @@
         <v>2.4</v>
       </c>
       <c r="N4">
-        <v>26.6</v>
+        <v>58.1</v>
+      </c>
+      <c r="O4">
+        <v>52</v>
       </c>
       <c r="P4">
-        <v>52</v>
+        <v>81.3</v>
       </c>
       <c r="Q4">
         <v>11.82</v>
@@ -815,10 +818,10 @@
         <v>881.79</v>
       </c>
       <c r="S4">
-        <v>58.1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>81.3</v>
+        <v>26.6</v>
       </c>
       <c r="V4">
         <v>143</v>
@@ -900,10 +903,13 @@
         <v>2.7</v>
       </c>
       <c r="N6">
-        <v>12.5</v>
+        <v>22.9</v>
+      </c>
+      <c r="O6">
+        <v>24.2</v>
       </c>
       <c r="P6">
-        <v>24.2</v>
+        <v>35.5</v>
       </c>
       <c r="Q6">
         <v>0.22</v>
@@ -912,10 +918,10 @@
         <v>2258</v>
       </c>
       <c r="S6">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>35.5</v>
+        <v>12.5</v>
       </c>
       <c r="V6">
         <v>141</v>
@@ -947,10 +953,13 @@
         <v>3.6</v>
       </c>
       <c r="N7">
-        <v>12.4</v>
+        <v>27.7</v>
+      </c>
+      <c r="O7">
+        <v>2.4</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q7">
         <v>0.32</v>
@@ -959,10 +968,10 @@
         <v>414.52</v>
       </c>
       <c r="S7">
-        <v>27.7</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>20.9</v>
+        <v>12.4</v>
       </c>
       <c r="V7">
         <v>87.2</v>
